--- a/tracking_forms/027_material_usage_tracking_request_form--tracking_forms.xlsx
+++ b/tracking_forms/027_material_usage_tracking_request_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1029,17 +1029,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>material_type_choices</t>
+          <t>unit_of_measurement_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ceramic</t>
+          <t>oz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ceramic</t>
+          <t>oz</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>lb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>oz</t>
+          <t>lb</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lb</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lb</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>cm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>cm</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>in</t>
         </is>
       </c>
     </row>
@@ -1170,29 +1170,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>mm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>unit_of_measurement_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>purchasing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Purchasing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>employee_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>purchasing</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Purchasing</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1272,27 +1272,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
